--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BGDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73A0787-3581-4D21-A9CD-91111CFCA519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BDD26A-13B7-4831-BC56-8028FDDF4FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1165,9 +1165,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1205,9 +1205,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1240,26 +1240,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1292,26 +1275,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -14666,126 +14632,96 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <f>'2020 Calculations'!B2</f>
-        <v>0.82698597951865516</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>'2020 Calculations'!C2</f>
-        <v>1.0000010797726713</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:AK9" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="K2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -14818,115 +14754,87 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:R3" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -14959,115 +14867,87 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15100,115 +14980,87 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15241,115 +15093,87 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15382,115 +15206,87 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15523,115 +15319,87 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15664,115 +15432,87 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" ref="G9:AK14" si="2">$B9</f>
         <v>0</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -15805,115 +15545,87 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -15946,115 +15658,87 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16078,127 +15762,96 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16222,126 +15875,96 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f>'2020 Calculations'!B3</f>
-        <v>0.71523111742153966</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <f>'2020 Calculations'!C3</f>
-        <v>1.0000010797726713</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16377,111 +16000,84 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16731,127 +16327,96 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" ref="G17:AK17" si="3">F17</f>
         <v>0</v>
       </c>
       <c r="H17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>

--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BGDPbES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AB2B1E-2998-B643-B477-BFCD12DF6B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294C88A3-4B51-9944-B44D-BBFD2A19C196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="354">
   <si>
     <t>Notes:</t>
   </si>
@@ -1092,13 +1092,19 @@
   </si>
   <si>
     <t>Bid Capacity Factor x Hours per Year[municipal solid waste es,newly built] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>BPS</t>
+  </si>
+  <si>
+    <t>https://esdm.go.id/assets/media/content/content-handbook-of-energy-and-economic-statistics-of-indonesia-2023.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1121,6 +1127,14 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1139,10 +1153,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1159,8 +1174,10 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1463,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1500,53 +1517,66 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
+      <c r="B9" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="B10" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
         <v>282</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{AE7F4E09-2A8B-E04F-9419-569707F06952}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -15193,128 +15223,97 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <f>'2020 Calculations'!B2</f>
-        <v>0.4676053280482092</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>'2020 Calculations'!C2</f>
-        <v>0.38725783384127582</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <f>'2020 Calculations'!D2</f>
-        <v>0.36299246943702695</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <f>'2020 Calculations'!E2</f>
-        <v>0.3235427622169037</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <f>'2020 Calculations'!F2</f>
-        <v>0.29232541068905493</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <f>'2020 Calculations'!G2</f>
-        <v>0.27314691896863608</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <f>'2020 Calculations'!H2</f>
-        <v>0.25748079133253876</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <f>'2020 Calculations'!I2</f>
-        <v>0.24465157886158045</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <f>'2020 Calculations'!J2</f>
-        <v>0.23436231549722417</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <f>'2020 Calculations'!K2</f>
-        <v>0.22580521187310026</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <f>'2020 Calculations'!L2</f>
-        <v>0.21860014601771138</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <f>'2020 Calculations'!M2</f>
-        <v>0.22690057069799094</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <f>'2020 Calculations'!N2</f>
-        <v>0.23520099537827049</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <f>'2020 Calculations'!O2</f>
-        <v>0.24350142005854736</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <f>'2020 Calculations'!P2</f>
-        <v>0.25180184473882694</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <f>'2020 Calculations'!Q2</f>
-        <v>0.26010226941910647</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <f>'2020 Calculations'!R2</f>
-        <v>0.26840269409938605</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <f>'2020 Calculations'!S2</f>
-        <v>0.27670311877966286</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <f>'2020 Calculations'!T2</f>
-        <v>0.28500354345994244</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <f>'2020 Calculations'!U2</f>
-        <v>0.29330396814022197</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <f>'2020 Calculations'!V2</f>
-        <v>0.30160439282049883</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <f>'2020 Calculations'!W2</f>
-        <v>0.30990481750077842</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <f>'2020 Calculations'!X2</f>
-        <v>0.318205242181058</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <f>'2020 Calculations'!Y2</f>
-        <v>0.32650566686133481</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <f>'2020 Calculations'!Z2</f>
-        <v>0.33480609154161439</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <f>'2020 Calculations'!AA2</f>
-        <v>0.34310651622189392</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <f>'2020 Calculations'!AB2</f>
-        <v>0.3514069409021735</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <f>'2020 Calculations'!AC2</f>
-        <v>0.35970736558245037</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <f>'2020 Calculations'!AD2</f>
-        <v>0.36800779026272995</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <f>'2020 Calculations'!AE2</f>
-        <v>0.37630821494300948</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <f>'2020 Calculations'!AF2</f>
-        <v>0.38460863962328634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -15346,115 +15345,87 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:R3" si="0">$B3</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="J3:AK9" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -15487,115 +15458,87 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -15628,115 +15571,87 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -15769,115 +15684,87 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -15910,115 +15797,87 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -16051,115 +15910,87 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -16192,115 +16023,87 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" ref="G9:AK14" si="2">$B9</f>
         <v>0</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16333,115 +16136,87 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16474,115 +16249,87 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16606,127 +16353,96 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -16750,128 +16466,97 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f>'2020 Calculations'!B3</f>
-        <v>0.40441541885250526</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <f>'2020 Calculations'!C3</f>
-        <v>0.38725783384127582</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <f>'2020 Calculations'!D3</f>
-        <v>0.36299246943702695</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <f>'2020 Calculations'!E3</f>
-        <v>0.3235427622169037</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <f>'2020 Calculations'!F3</f>
-        <v>0.29232541068905493</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <f>'2020 Calculations'!G3</f>
-        <v>0.27314691896863608</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <f>'2020 Calculations'!H3</f>
-        <v>0.25748079133253876</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <f>'2020 Calculations'!I3</f>
-        <v>0.24465157886158045</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <f>'2020 Calculations'!J3</f>
-        <v>0.23436231549722417</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <f>'2020 Calculations'!K3</f>
-        <v>0.22580521187310026</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <f>'2020 Calculations'!L3</f>
-        <v>0.21860014601771138</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <f>'2020 Calculations'!M3</f>
-        <v>0.22690057069799094</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <f>'2020 Calculations'!N3</f>
-        <v>0.23520099537827049</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <f>'2020 Calculations'!O3</f>
-        <v>0.24350142005854736</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <f>'2020 Calculations'!P3</f>
-        <v>0.25180184473882694</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <f>'2020 Calculations'!Q3</f>
-        <v>0.26010226941910647</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <f>'2020 Calculations'!R3</f>
-        <v>0.26840269409938605</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <f>'2020 Calculations'!S3</f>
-        <v>0.27670311877966286</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <f>'2020 Calculations'!T3</f>
-        <v>0.28500354345994244</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <f>'2020 Calculations'!U3</f>
-        <v>0.29330396814022197</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <f>'2020 Calculations'!V3</f>
-        <v>0.30160439282049883</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <f>'2020 Calculations'!W3</f>
-        <v>0.30990481750077842</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <f>'2020 Calculations'!X3</f>
-        <v>0.318205242181058</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <f>'2020 Calculations'!Y3</f>
-        <v>0.32650566686133481</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <f>'2020 Calculations'!Z3</f>
-        <v>0.33480609154161439</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <f>'2020 Calculations'!AA3</f>
-        <v>0.34310651622189392</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <f>'2020 Calculations'!AB3</f>
-        <v>0.3514069409021735</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <f>'2020 Calculations'!AC3</f>
-        <v>0.35970736558245037</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <f>'2020 Calculations'!AD3</f>
-        <v>0.36800779026272995</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <f>'2020 Calculations'!AE3</f>
-        <v>0.37630821494300948</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <f>'2020 Calculations'!AF3</f>
-        <v>0.38460863962328634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -16906,111 +16591,84 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -17260,135 +16918,101 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" ref="G17:AK17" si="3">F17</f>
         <v>0</v>
       </c>
       <c r="H17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="K13:Q13 R13:AK13" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BGDPbES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294C88A3-4B51-9944-B44D-BBFD2A19C196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD5E1BB-0AC2-7C4D-B848-D5A362FE7BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1157,7 +1157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1175,6 +1175,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -15083,14 +15084,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:BE17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="32">
+    <row r="1" spans="1:57" ht="32">
       <c r="A1" s="3" t="s">
         <v>25</v>
       </c>
@@ -15202,1812 +15203,2832 @@
       <c r="AK1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:37">
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+      <c r="B2" s="9">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>0</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9">
+        <v>0</v>
+      </c>
+      <c r="O2" s="9">
+        <v>0</v>
+      </c>
+      <c r="P2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>0</v>
+      </c>
+      <c r="S2" s="9">
+        <v>0</v>
+      </c>
+      <c r="T2" s="9">
+        <v>0</v>
+      </c>
+      <c r="U2" s="9">
+        <v>0</v>
+      </c>
+      <c r="V2" s="9">
+        <v>0</v>
+      </c>
+      <c r="W2" s="9">
+        <v>0</v>
+      </c>
+      <c r="X2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
+      <c r="B3" s="9">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
+      </c>
+      <c r="S3" s="9">
+        <v>0</v>
+      </c>
+      <c r="T3" s="9">
+        <v>0</v>
+      </c>
+      <c r="U3" s="9">
+        <v>0</v>
+      </c>
+      <c r="V3" s="9">
+        <v>0</v>
+      </c>
+      <c r="W3" s="9">
+        <v>0</v>
+      </c>
+      <c r="X3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57">
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9">
+        <v>0</v>
+      </c>
+      <c r="V4" s="9">
+        <v>0</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37">
+      <c r="B5" s="9">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57">
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
+      <c r="B6" s="9">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9">
+        <v>0</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9">
+        <v>0</v>
+      </c>
+      <c r="T7" s="9">
+        <v>0</v>
+      </c>
+      <c r="U7" s="9">
+        <v>0</v>
+      </c>
+      <c r="V7" s="9">
+        <v>0</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57">
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57">
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57">
       <c r="A12" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37">
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57">
       <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9">
+        <v>0</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57">
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9">
+        <v>0</v>
+      </c>
+      <c r="V14" s="9">
+        <v>0</v>
+      </c>
+      <c r="W14" s="9">
+        <v>0</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57">
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57">
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
+        <v>0</v>
+      </c>
+      <c r="S16" s="9">
+        <v>0</v>
+      </c>
+      <c r="T16" s="9">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0</v>
+      </c>
+      <c r="W16" s="9">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD16" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:57">
       <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
+        <v>0</v>
+      </c>
+      <c r="S17" s="9">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9">
+        <v>0</v>
+      </c>
+      <c r="V17" s="9">
+        <v>0</v>
+      </c>
+      <c r="W17" s="9">
+        <v>0</v>
+      </c>
+      <c r="X17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="9">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="9">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="9">
+        <v>0</v>
+      </c>
+      <c r="BD17" s="9">
+        <v>0</v>
+      </c>
+      <c r="BE17" s="9">
         <v>0</v>
       </c>
     </row>
